--- a/WS2.0/downloads/author details/arxiv_hiv_authors.xlsx
+++ b/WS2.0/downloads/author details/arxiv_hiv_authors.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="Authors" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Authors'!$A$1:$D$16</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +27,45 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9FAFB"/>
+        <bgColor rgb="00F9FAFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +73,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E5E7EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E5E7EB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E5E7EB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E5E7EB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,530 +467,369 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="171" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="65" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>PDF File Name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Source Journal</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Paper Title</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Author Name</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Email ID</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>DOI</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>arxiv_paper_2.pdf</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Too sick for surveillance: Can federal HIV service data improve federal HIV surveillance efforts?</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Nick Williams</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>nick.williams@nih.gov</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>http://arxiv.org/abs/2304.10023v1</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>arxiv_paper_3.pdf</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Evaluating the potential of HIV self-testing to reduce HIV incidence in EHE districts: a modeling study</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Alex Viguerie</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Alexander Viguerie</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>alexander.viguerie@uniurb.it</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>http://arxiv.org/abs/2504.15807v1</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>arxiv_paper_5.pdf</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Estimation of Contextual Exposure to HIV from GPS Data</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Adrian Dobra</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Adobra</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>adobra@uw.edu</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>http://arxiv.org/abs/2512.11159v1</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>arxiv_paper_7.pdf</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Quantum Approximate Optimization Algorithm for Spatiotemporal Forecasting of HIV Clusters</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Don Roosan</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Roosand</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>roosand@merrimack.edu</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>http://arxiv.org/abs/2507.00848v1</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>arxiv_paper_7.pdf</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Quantum Approximate Optimization Algorithm for Spatiotemporal Forecasting of HIV Clusters</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Saif Nirzhor</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>saif.nirzhor@utsouthwestern.edu</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>http://arxiv.org/abs/2507.00848v1</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>arxiv_paper_7.pdf</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Quantum Approximate Optimization Algorithm for Spatiotemporal Forecasting of HIV Clusters</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Rubayat Khan</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>rubayat.khan@unmc.edu</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>http://arxiv.org/abs/2507.00848v1</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>arxiv_paper_7.pdf</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Quantum Approximate Optimization Algorithm for Spatiotemporal Forecasting of HIV Clusters</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Fahmida Hai</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Fahmida</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>fahmida@tekurai.com</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>http://arxiv.org/abs/2507.00848v1</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>arxiv_paper_7.pdf</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Quantum Approximate Optimization Algorithm for Spatiotemporal Forecasting of HIV Clusters</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Fahmida Hai</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Haider</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>haider@uga.edu</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>http://arxiv.org/abs/2507.00848v1</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>arxiv_paper_8.pdf</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>A Likelihood Approach to Incorporating Self-Report Data in HIV Recency Classification</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Wenlong Yang</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Wenlong</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>wenlong@psu.edu</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>http://arxiv.org/abs/2309.02430v2</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>arxiv_paper_8.pdf</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>A Likelihood Approach to Incorporating Self-Report Data in HIV Recency Classification</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Danping Liu</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>danping.liu@nih.gov</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>http://arxiv.org/abs/2309.02430v2</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>arxiv_paper_8.pdf</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>A Likelihood Approach to Incorporating Self-Report Data in HIV Recency Classification</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>lub14@psu.edu</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>http://arxiv.org/abs/2309.02430v2</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>arxiv_paper_8.pdf</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>A Likelihood Approach to Incorporating Self-Report Data in HIV Recency Classification</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>rzli@psu.edu</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>http://arxiv.org/abs/2309.02430v2</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>arxiv_paper_9.pdf</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>HIV Client Perspectives on Digital Health in Malawi</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Jacqueline Madalitso Huwa</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Jhuwa</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>jhuwa@lighthouse.org.mw</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1145/3613904.3642245</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>arxiv_paper_9.pdf</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>HIV Client Perspectives on Digital Health in Malawi</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>ckamamia@lighthouse.org.mw</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>https://doi.org/10.1145/3613904.3642245</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>arxiv_paper_10.pdf</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>The effects of HIV self-testing on HIV incidence and awareness of status among men who have sex with men in the United States: Insights from a novel compartmental model</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>xjm9@cdc.gov</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>http://arxiv.org/abs/2404.04222v1</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/WS2.0/downloads/author details/arxiv_hiv_authors.xlsx
+++ b/WS2.0/downloads/author details/arxiv_hiv_authors.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Authors" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Authors'!$A$1:$D$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Authors'!$A$1:$E$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -99,8 +99,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -467,13 +473,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -494,6 +501,11 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>DOI</t>
         </is>
       </c>
@@ -514,29 +526,39 @@
           <t>nick.williams@nih.gov</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>http://arxiv.org/abs/2304.10023v1</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Evaluating the potential of HIV self-testing to reduce HIV incidence in EHE districts: a modeling study</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Alexander Viguerie</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>alexander.viguerie@uniurb.it</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>http://arxiv.org/abs/2504.15807v1</t>
         </is>
@@ -558,29 +580,39 @@
           <t>adobra@uw.edu</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>http://arxiv.org/abs/2512.11159v1</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Quantum Approximate Optimization Algorithm for Spatiotemporal Forecasting of HIV Clusters</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Roosand</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>roosand@merrimack.edu</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>http://arxiv.org/abs/2507.00848v1</t>
         </is>
@@ -602,29 +634,39 @@
           <t>saif.nirzhor@utsouthwestern.edu</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>http://arxiv.org/abs/2507.00848v1</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Quantum Approximate Optimization Algorithm for Spatiotemporal Forecasting of HIV Clusters</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Rubayat Khan</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>rubayat.khan@unmc.edu</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>http://arxiv.org/abs/2507.00848v1</t>
         </is>
@@ -646,29 +688,39 @@
           <t>fahmida@tekurai.com</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>http://arxiv.org/abs/2507.00848v1</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Quantum Approximate Optimization Algorithm for Spatiotemporal Forecasting of HIV Clusters</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Haider</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>haider@uga.edu</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>http://arxiv.org/abs/2507.00848v1</t>
         </is>
@@ -690,29 +742,39 @@
           <t>wenlong@psu.edu</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>http://arxiv.org/abs/2309.02430v2</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>A Likelihood Approach to Incorporating Self-Report Data in HIV Recency Classification</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Danping Liu</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>danping.liu@nih.gov</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>http://arxiv.org/abs/2309.02430v2</t>
         </is>
@@ -734,29 +796,39 @@
           <t>lub14@psu.edu</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>http://arxiv.org/abs/2309.02430v2</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>A Likelihood Approach to Incorporating Self-Report Data in HIV Recency Classification</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>rzli@psu.edu</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>http://arxiv.org/abs/2309.02430v2</t>
         </is>
@@ -778,29 +850,39 @@
           <t>jhuwa@lighthouse.org.mw</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1145/3613904.3642245</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>HIV Client Perspectives on Digital Health in Malawi</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>ckamamia@lighthouse.org.mw</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>https://doi.org/10.1145/3613904.3642245</t>
         </is>
@@ -822,14 +904,19 @@
           <t>xjm9@cdc.gov</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>http://arxiv.org/abs/2404.04222v1</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D16"/>
+  <autoFilter ref="A1:E16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>